--- a/Excel/Tabella_strutturata.xlsx
+++ b/Excel/Tabella_strutturata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annar\OneDrive\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F35FF3E-8CBE-4C2A-9290-9F8975CC785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00428EED-63DE-481D-B190-275BC05A51C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2946FDA1-133B-4395-9958-95A55DD29756}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{2946FDA1-133B-4395-9958-95A55DD29756}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="130">
   <si>
     <t>Per la pace d'Italia</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Item_1.html</t>
+  </si>
+  <si>
+    <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Item_2.html</t>
   </si>
 </sst>
 </file>
@@ -473,10 +479,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -840,29 +845,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EA7E1B-6996-400C-B4A3-65BE72819B2E}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="48.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>105</v>
       </c>
@@ -918,14 +923,14 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -937,7 +942,7 @@
       <c r="F2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -946,10 +951,10 @@
       <c r="I2" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>96</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -958,10 +963,10 @@
       <c r="M2">
         <v>13495</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>92</v>
       </c>
       <c r="P2" t="s">
@@ -974,14 +979,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -993,7 +998,7 @@
       <c r="F3" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1002,10 +1007,10 @@
       <c r="I3" t="s">
         <v>84</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>96</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1014,10 +1019,10 @@
       <c r="M3">
         <v>22877</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>92</v>
       </c>
       <c r="P3" t="s">
@@ -1030,14 +1035,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1049,7 +1054,7 @@
       <c r="F4" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -1058,10 +1063,10 @@
       <c r="I4" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" t="s">
         <v>96</v>
       </c>
       <c r="L4" s="1" t="s">
@@ -1070,10 +1075,10 @@
       <c r="M4">
         <v>13480</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" t="s">
         <v>92</v>
       </c>
       <c r="P4" t="s">
@@ -1086,14 +1091,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1105,7 +1110,7 @@
       <c r="F5" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1114,10 +1119,10 @@
       <c r="I5" t="s">
         <v>86</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
         <v>96</v>
       </c>
       <c r="L5" s="1" t="s">
@@ -1126,10 +1131,10 @@
       <c r="M5">
         <v>13504</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" t="s">
         <v>92</v>
       </c>
       <c r="P5" t="s">
@@ -1142,14 +1147,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1161,7 +1166,7 @@
       <c r="F6" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1170,10 +1175,10 @@
       <c r="I6" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" t="s">
         <v>96</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -1182,10 +1187,10 @@
       <c r="M6">
         <v>22956</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" t="s">
         <v>92</v>
       </c>
       <c r="P6" t="s">
@@ -1198,14 +1203,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1217,7 +1222,7 @@
       <c r="F7" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -1226,10 +1231,10 @@
       <c r="I7" t="s">
         <v>87</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" t="s">
         <v>97</v>
       </c>
       <c r="L7" s="1" t="s">
@@ -1238,10 +1243,10 @@
       <c r="M7">
         <v>30</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" t="s">
         <v>93</v>
       </c>
       <c r="P7" t="s">
@@ -1251,17 +1256,17 @@
         <v>103</v>
       </c>
       <c r="R7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1273,7 +1278,7 @@
       <c r="F8" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1282,10 +1287,10 @@
       <c r="I8" t="s">
         <v>84</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" t="s">
         <v>96</v>
       </c>
       <c r="L8" s="1" t="s">
@@ -1294,10 +1299,10 @@
       <c r="M8">
         <v>22589</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" t="s">
         <v>92</v>
       </c>
       <c r="P8" t="s">
@@ -1310,14 +1315,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1329,7 +1334,7 @@
       <c r="F9" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -1338,10 +1343,10 @@
       <c r="I9" t="s">
         <v>84</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" t="s">
         <v>96</v>
       </c>
       <c r="L9" s="1" t="s">
@@ -1350,10 +1355,10 @@
       <c r="M9">
         <v>22884</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" t="s">
         <v>92</v>
       </c>
       <c r="P9" t="s">
@@ -1366,14 +1371,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1385,7 +1390,7 @@
       <c r="F10" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -1394,10 +1399,10 @@
       <c r="I10" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" t="s">
         <v>96</v>
       </c>
       <c r="L10" s="1" t="s">
@@ -1406,10 +1411,10 @@
       <c r="M10">
         <v>22412</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" t="s">
         <v>92</v>
       </c>
       <c r="P10" t="s">
@@ -1422,14 +1427,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1441,7 +1446,7 @@
       <c r="F11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -1450,10 +1455,10 @@
       <c r="I11" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" t="s">
         <v>96</v>
       </c>
       <c r="L11" s="1" t="s">
@@ -1462,10 +1467,10 @@
       <c r="M11">
         <v>22505</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" t="s">
         <v>92</v>
       </c>
       <c r="P11" t="s">
@@ -1478,14 +1483,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1497,7 +1502,7 @@
       <c r="F12" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" t="s">
         <v>29</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -1506,10 +1511,10 @@
       <c r="I12" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" t="s">
         <v>36</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" t="s">
         <v>96</v>
       </c>
       <c r="L12" s="1" t="s">
@@ -1518,10 +1523,10 @@
       <c r="M12">
         <v>22453</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O12" t="s">
         <v>92</v>
       </c>
       <c r="P12" t="s">
@@ -1534,14 +1539,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1553,7 +1558,7 @@
       <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -1562,10 +1567,10 @@
       <c r="I13" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" t="s">
         <v>97</v>
       </c>
       <c r="L13" s="1" t="s">
@@ -1574,10 +1579,10 @@
       <c r="M13">
         <v>102</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" t="s">
         <v>38</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" t="s">
         <v>93</v>
       </c>
       <c r="P13" t="s">
@@ -1590,14 +1595,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1609,7 +1614,7 @@
       <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -1618,10 +1623,10 @@
       <c r="I14" t="s">
         <v>85</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" t="s">
         <v>96</v>
       </c>
       <c r="L14" s="1" t="s">
@@ -1630,10 +1635,10 @@
       <c r="M14">
         <v>22649</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O14" t="s">
         <v>92</v>
       </c>
       <c r="P14" t="s">
@@ -1646,14 +1651,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1665,7 +1670,7 @@
       <c r="F15" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -1674,10 +1679,10 @@
       <c r="I15" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" t="s">
         <v>96</v>
       </c>
       <c r="L15" s="1" t="s">
@@ -1686,10 +1691,10 @@
       <c r="M15">
         <v>22377</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" t="s">
         <v>39</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" t="s">
         <v>92</v>
       </c>
       <c r="P15" t="s">
@@ -1702,14 +1707,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1721,7 +1726,7 @@
       <c r="F16" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="1" t="s">
@@ -1730,10 +1735,10 @@
       <c r="I16" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" t="s">
         <v>36</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" t="s">
         <v>96</v>
       </c>
       <c r="L16" s="1" t="s">
@@ -1742,10 +1747,10 @@
       <c r="M16">
         <v>22205</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" t="s">
         <v>92</v>
       </c>
       <c r="P16" t="s">
@@ -1758,14 +1763,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1777,7 +1782,7 @@
       <c r="F17" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -1786,10 +1791,10 @@
       <c r="I17" t="s">
         <v>85</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" t="s">
         <v>36</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" t="s">
         <v>96</v>
       </c>
       <c r="L17" s="1" t="s">
@@ -1798,10 +1803,10 @@
       <c r="M17">
         <v>22603</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" t="s">
         <v>39</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="O17" t="s">
         <v>92</v>
       </c>
       <c r="P17" t="s">
@@ -1811,17 +1816,17 @@
         <v>125</v>
       </c>
       <c r="R17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1833,7 +1838,7 @@
       <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -1842,10 +1847,10 @@
       <c r="I18" t="s">
         <v>86</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" t="s">
         <v>98</v>
       </c>
       <c r="L18" s="1" t="s">
@@ -1854,10 +1859,10 @@
       <c r="M18" t="s">
         <v>91</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" t="s">
         <v>94</v>
       </c>
       <c r="P18" t="s">
@@ -1870,14 +1875,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1889,7 +1894,7 @@
       <c r="F19" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" t="s">
         <v>28</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -1898,10 +1903,10 @@
       <c r="I19" t="s">
         <v>89</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" t="s">
         <v>99</v>
       </c>
       <c r="L19" s="1" t="s">
@@ -1910,10 +1915,10 @@
       <c r="M19" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" t="s">
         <v>38</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="O19" t="s">
         <v>95</v>
       </c>
       <c r="P19" t="s">
@@ -1965,6 +1970,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AADF751550A837458F675DC0EDA2E01A" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0f2efc615ea7c2165c722a97587b1e6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ec621e79-30a5-40a0-82cf-20feb35471e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05d8eab6b1e18d03b34a363908ce1f25" ns3:_="">
     <xsd:import namespace="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
@@ -2120,24 +2142,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C9553B-5F85-473C-98D5-03A8F2F0F021}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29F4E236-4113-44C1-AC23-33F41F71ADE1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37AD9784-D441-41AE-9CD2-D772E3B00814}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2153,28 +2182,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29F4E236-4113-44C1-AC23-33F41F71ADE1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C9553B-5F85-473C-98D5-03A8F2F0F021}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>